--- a/backend-java/ai-service/src/test/resources/corpus-test/CORPUS_TEST/00_COMMUN/DICTIONNAIRE_UNIQUE_VARIABLES.xlsx
+++ b/backend-java/ai-service/src/test/resources/corpus-test/CORPUS_TEST/00_COMMUN/DICTIONNAIRE_UNIQUE_VARIABLES.xlsx
@@ -47,6 +47,11 @@
           <t xml:space="preserve">Signification (texte du cabinet)</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Libellé du champ à l'écran (proposé, à valider)</t>
+        </is>
+      </c>
       <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Nom canonique retenu par la plateforme</t>
@@ -64,6 +69,11 @@
           <t xml:space="preserve">variable de test</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dénomination de la société</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">$DENOMINATION</t>
@@ -81,6 +91,11 @@
           <t xml:space="preserve">variable de test</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CAPITAL_SOCIAL</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">$CAPITAL_SOCIAL</t>
@@ -98,6 +113,11 @@
           <t xml:space="preserve">variable de test</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SIEGE_SOCIAL</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">$SIEGE_SOCIAL</t>
@@ -115,6 +135,11 @@
           <t xml:space="preserve">variable de test</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ASSOCIE_NOM</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">$ASSOCIE_NOM</t>
@@ -132,6 +157,11 @@
           <t xml:space="preserve">variable de test</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ASSOCIE_PARTS</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">$ASSOCIE_PARTS</t>
@@ -149,6 +179,11 @@
           <t xml:space="preserve">variable de test</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GERANT_UNIQUE</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">$GERANT_UNIQUE</t>
@@ -166,6 +201,11 @@
           <t xml:space="preserve">variable de test</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GERANT_NOM</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">$GERANT_NOM</t>
@@ -183,9 +223,2346 @@
           <t xml:space="preserve">variable de test</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lieu de signature</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">$LIEU_SIGNATURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$ACQUEREUR_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACQUEREUR_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$ACQUEREUR_RC_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$APPORTEUR_ICE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">APPORTEUR_ICE</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$APPORTEUR_ICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$APPORTEUR_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">APPORTEUR_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$APPORTEUR_RC_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$APPORT_BENEFICIAIRE_ICE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">APPORT_BENEFICIAIRE_ICE</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$APPORT_BENEFICIAIRE_ICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$APPORT_BENEFICIAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">APPORT_BENEFICIAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$APPORT_BENEFICIAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$APPORT_FONDS_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">APPORT_FONDS_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$APPORT_FONDS_RC_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$APPORT_ORIGINE_ENREGISTREMENT_DATE</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">APPORT_ORIGINE_ENREGISTREMENT_DATE</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$APPORT_ORIGINE_ENREGISTREMENT_DATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$ASSOCIE_IDENTIFIANT_FISCAL</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ASSOCIE_IDENTIFIANT_FISCAL</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$ASSOCIE_IDENTIFIANT_FISCAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$ASSOCIE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ASSOCIE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$ASSOCIE_RC_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$ASSOCIE_RETRAYANT_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ASSOCIE_RETRAYANT_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$ASSOCIE_RETRAYANT_RC_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$ATTESTATION_TITRES_IDENTIFIANT_FISCAL</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ATTESTATION_TITRES_IDENTIFIANT_FISCAL</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$ATTESTATION_TITRES_IDENTIFIANT_FISCAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$BAILLEUR_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BAILLEUR_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$BAILLEUR_RC_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$BE_IDENTIFIANT_FISCAL</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BE_IDENTIFIANT_FISCAL</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$BE_IDENTIFIANT_FISCAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$BE_INTERMEDIAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BE_INTERMEDIAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$BE_INTERMEDIAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$BONI_ASSOCIE_IDENTIFIANT_FISCAL</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BONI_ASSOCIE_IDENTIFIANT_FISCAL</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$BONI_ASSOCIE_IDENTIFIANT_FISCAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$BONI_ASSOCIE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BONI_ASSOCIE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$BONI_ASSOCIE_RC_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$BONI_BENEFICIAIRE_IDENTIFIANT_FISCAL</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BONI_BENEFICIAIRE_IDENTIFIANT_FISCAL</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$BONI_BENEFICIAIRE_IDENTIFIANT_FISCAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$BONI_BENEFICIAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BONI_BENEFICIAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$BONI_BENEFICIAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$BULLETIN_OFFICIEL_DATE_PUBLICATION</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BULLETIN_OFFICIEL_DATE_PUBLICATION</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$BULLETIN_OFFICIEL_DATE_PUBLICATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$BULLETIN_OFFICIEL_NUMERO</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BULLETIN_OFFICIEL_NUMERO</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$BULLETIN_OFFICIEL_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$CERTIFICAT_NEGATIF_CADUCITE_DATE</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CERTIFICAT_NEGATIF_CADUCITE_DATE</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$CERTIFICAT_NEGATIF_CADUCITE_DATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$CERTIFICAT_NEGATIF_DATE</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CERTIFICAT_NEGATIF_DATE</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$CERTIFICAT_NEGATIF_DATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$CERTIFICAT_NEGATIF_NUMERO</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CERTIFICAT_NEGATIF_NUMERO</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$CERTIFICAT_NEGATIF_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$CESSION_CEDANT_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CESSION_CEDANT_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$CESSION_CEDANT_RC_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$CESSION_CESSIONNAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CESSION_CESSIONNAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$CESSION_CESSIONNAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$CESSION_ENREGISTREMENT_DATE</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CESSION_ENREGISTREMENT_DATE</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$CESSION_ENREGISTREMENT_DATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$CNDP_RECEPISSE_NUMERO</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CNDP_RECEPISSE_NUMERO</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$CNDP_RECEPISSE_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$CNSS_NUMERO</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CNSS_NUMERO</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$CNSS_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$COMPTE_COURANT_ASSOCIE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMPTE_COURANT_ASSOCIE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$COMPTE_COURANT_ASSOCIE_RC_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$CREANCIER_ICE</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CREANCIER_ICE</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$CREANCIER_ICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$CREANCIER_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CREANCIER_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$CREANCIER_RC_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$DATE_DEPOT_LEGAL</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DATE_DEPOT_LEGAL</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$DATE_DEPOT_LEGAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$DATE_IMMATRICULATION</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DATE_IMMATRICULATION</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$DATE_IMMATRICULATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$DATE_IMMATRICULATION_NOUVELLE</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DATE_IMMATRICULATION_NOUVELLE</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$DATE_IMMATRICULATION_NOUVELLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$DELEGATAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DELEGATAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$DELEGATAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$DEPOT_GREFFE_DATE</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEPOT_GREFFE_DATE</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$DEPOT_GREFFE_DATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$DEPOT_LEGAL_NUMERO</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEPOT_LEGAL_NUMERO</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$DEPOT_LEGAL_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$DISSOLUTION_BO_DATE_PARUTION</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISSOLUTION_BO_DATE_PARUTION</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$DISSOLUTION_BO_DATE_PARUTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$DISSOLUTION_DEPOT_GREFFE_DATE</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISSOLUTION_DEPOT_GREFFE_DATE</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$DISSOLUTION_DEPOT_GREFFE_DATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$DISSOLUTION_DEPOT_GREFFE_NUMERO</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISSOLUTION_DEPOT_GREFFE_NUMERO</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$DISSOLUTION_DEPOT_GREFFE_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$DIVIDENDE_BENEFICIAIRE_ICE</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIVIDENDE_BENEFICIAIRE_ICE</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$DIVIDENDE_BENEFICIAIRE_ICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$DIVIDENDE_BENEFICIAIRE_IDENTIFIANT_FISCAL</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIVIDENDE_BENEFICIAIRE_IDENTIFIANT_FISCAL</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$DIVIDENDE_BENEFICIAIRE_IDENTIFIANT_FISCAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$DIVIDENDE_BENEFICIAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIVIDENDE_BENEFICIAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$DIVIDENDE_BENEFICIAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$DOMICILIATAIRE_ICE</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DOMICILIATAIRE_ICE</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$DOMICILIATAIRE_ICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$DOMICILIATAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DOMICILIATAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$DOMICILIATAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$DPS_BENEFICIAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DPS_BENEFICIAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$DPS_BENEFICIAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$ENREGISTREMENT_ACTE_DATE</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ENREGISTREMENT_ACTE_DATE</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$ENREGISTREMENT_ACTE_DATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$ENREGISTREMENT_ACTE_REFERENCE</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ENREGISTREMENT_ACTE_REFERENCE</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$ENREGISTREMENT_ACTE_REFERENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$ENREGISTREMENT_LIEU</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ENREGISTREMENT_LIEU</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$ENREGISTREMENT_LIEU</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$ETAB_IDENTIFIANT_TP</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETAB_IDENTIFIANT_TP</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$ETAB_IDENTIFIANT_TP</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$ETAB_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETAB_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$ETAB_RC_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$FONDS_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FONDS_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$FONDS_RC_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$FUSION_SOCIETE_ICE</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FUSION_SOCIETE_ICE</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$FUSION_SOCIETE_ICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$FUSION_SOCIETE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FUSION_SOCIETE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$FUSION_SOCIETE_RC_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$GARANTIE_BENEFICIAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GARANTIE_BENEFICIAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$GARANTIE_BENEFICIAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$GARANTIE_DEBITEUR_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GARANTIE_DEBITEUR_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$GARANTIE_DEBITEUR_RC_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$ICE</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ICE</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$ICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$IDENTIFIANT_FISCAL</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IDENTIFIANT_FISCAL</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$IDENTIFIANT_FISCAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$IDENTIFIANT_FISCAL_NOUVEAU</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IDENTIFIANT_FISCAL_NOUVEAU</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$IDENTIFIANT_FISCAL_NOUVEAU</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$IDENTIFIANT_TP</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IDENTIFIANT_TP</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$IDENTIFIANT_TP</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$INVESTISSEMENT_DETENU_IMMATRICULATION_NUMERO</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INVESTISSEMENT_DETENU_IMMATRICULATION_NUMERO</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$INVESTISSEMENT_DETENU_IMMATRICULATION_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$LIQUIDATEUR_ICE</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIQUIDATEUR_ICE</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$LIQUIDATEUR_ICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$LIQUIDATEUR_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIQUIDATEUR_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$LIQUIDATEUR_RC_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$LIQUIDATION_CLOTURE_BO_DATE_PARUTION</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIQUIDATION_CLOTURE_BO_DATE_PARUTION</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$LIQUIDATION_CLOTURE_BO_DATE_PARUTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$LIQUIDATION_CLOTURE_DEPOT_GREFFE_DATE</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIQUIDATION_CLOTURE_DEPOT_GREFFE_DATE</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$LIQUIDATION_CLOTURE_DEPOT_GREFFE_DATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$LIQUIDATION_CLOTURE_ENREGISTREMENT_DATE</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIQUIDATION_CLOTURE_ENREGISTREMENT_DATE</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$LIQUIDATION_CLOTURE_ENREGISTREMENT_DATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$LIQUIDATION_CLOTURE_ENREGISTREMENT_REFERENCE</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIQUIDATION_CLOTURE_ENREGISTREMENT_REFERENCE</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$LIQUIDATION_CLOTURE_ENREGISTREMENT_REFERENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$LOCATION_GERANCE_BAILLEUR_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOCATION_GERANCE_BAILLEUR_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$LOCATION_GERANCE_BAILLEUR_RC_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$LOCATION_GERANCE_LOCATAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOCATION_GERANCE_LOCATAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$LOCATION_GERANCE_LOCATAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$MOUVEMENT_ENREGISTREMENT_REFERENCE</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOUVEMENT_ENREGISTREMENT_REFERENCE</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$MOUVEMENT_ENREGISTREMENT_REFERENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$NANTISSEMENT_CONSTITUANT_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NANTISSEMENT_CONSTITUANT_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$NANTISSEMENT_CONSTITUANT_RC_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$NANTISSEMENT_CREANCIER_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NANTISSEMENT_CREANCIER_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$NANTISSEMENT_CREANCIER_RC_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$POUVOIR_MANDATAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POUVOIR_MANDATAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$POUVOIR_MANDATAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$QUITUS_FISCAL_AUTORITE</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QUITUS_FISCAL_AUTORITE</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$QUITUS_FISCAL_AUTORITE</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$QUITUS_FISCAL_DATE</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QUITUS_FISCAL_DATE</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$QUITUS_FISCAL_DATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$QUITUS_FISCAL_REFERENCE</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QUITUS_FISCAL_REFERENCE</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$QUITUS_FISCAL_REFERENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$RC_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$RC_NUMERO_NOUVEAU</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RC_NUMERO_NOUVEAU</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$RC_NUMERO_NOUVEAU</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SALARIE_CNSS_IMMATRICULATION</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SALARIE_CNSS_IMMATRICULATION</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SALARIE_CNSS_IMMATRICULATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SCISSION_BENEFICIAIRE_ICE</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SCISSION_BENEFICIAIRE_ICE</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SCISSION_BENEFICIAIRE_ICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SCISSION_BENEFICIAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SCISSION_BENEFICIAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SCISSION_BENEFICIAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SCISSION_SCINDEE_ICE</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SCISSION_SCINDEE_ICE</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SCISSION_SCINDEE_ICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SCISSION_SCINDEE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SCISSION_SCINDEE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SCISSION_SCINDEE_RC_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SOUSCRIPTEUR_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SOUSCRIPTEUR_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SOUSCRIPTEUR_RC_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_BAIL_ENREGISTREMENT_DATE</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUCCURSALE_BAIL_ENREGISTREMENT_DATE</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_BAIL_ENREGISTREMENT_DATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_BAIL_ENREGISTREMENT_REFERENCE</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUCCURSALE_BAIL_ENREGISTREMENT_REFERENCE</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_BAIL_ENREGISTREMENT_REFERENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_CNSS_NUMERO</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUCCURSALE_CNSS_NUMERO</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_CNSS_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_DATE_IMMATRICULATION</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUCCURSALE_DATE_IMMATRICULATION</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_DATE_IMMATRICULATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_DECISION_ENREGISTREMENT_DATE</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUCCURSALE_DECISION_ENREGISTREMENT_DATE</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_DECISION_ENREGISTREMENT_DATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_DECISION_ENREGISTREMENT_REFERENCE</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUCCURSALE_DECISION_ENREGISTREMENT_REFERENCE</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_DECISION_ENREGISTREMENT_REFERENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_DOMICILIATAIRE_ICE</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUCCURSALE_DOMICILIATAIRE_ICE</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_DOMICILIATAIRE_ICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_DOMICILIATAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUCCURSALE_DOMICILIATAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_DOMICILIATAIRE_RC_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_ETABLISSEMENT_ORIGINE_IDENTIFIANT_TP</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUCCURSALE_ETABLISSEMENT_ORIGINE_IDENTIFIANT_TP</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_ETABLISSEMENT_ORIGINE_IDENTIFIANT_TP</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_ETRANGERE_IMMATRICULATION_DATE</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUCCURSALE_ETRANGERE_IMMATRICULATION_DATE</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_ETRANGERE_IMMATRICULATION_DATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_ETRANGERE_IMMATRICULATION_NUMERO</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUCCURSALE_ETRANGERE_IMMATRICULATION_NUMERO</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_ETRANGERE_IMMATRICULATION_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_ETRANGERE_IMMATRICULATION_REGISTRE</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUCCURSALE_ETRANGERE_IMMATRICULATION_REGISTRE</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_ETRANGERE_IMMATRICULATION_REGISTRE</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_ICE</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUCCURSALE_ICE</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_ICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_IDENTIFIANT_FISCAL</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUCCURSALE_IDENTIFIANT_FISCAL</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_IDENTIFIANT_FISCAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_IDENTIFIANT_TP</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUCCURSALE_IDENTIFIANT_TP</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_IDENTIFIANT_TP</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_IMMATRICULATION_DATE</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUCCURSALE_IMMATRICULATION_DATE</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_IMMATRICULATION_DATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUCCURSALE_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_RC_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_REGROUPEMENT_ETABLISSEMENT_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUCCURSALE_REGROUPEMENT_ETABLISSEMENT_RC_NUMERO</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_REGROUPEMENT_ETABLISSEMENT_RC_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_TP_CERTIFICAT_DATE</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUCCURSALE_TP_CERTIFICAT_DATE</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_TP_CERTIFICAT_DATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_TP_CERTIFICAT_NUMERO</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUCCURSALE_TP_CERTIFICAT_NUMERO</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_TP_CERTIFICAT_NUMERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_TP_SERVICE_EMETTEUR</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUCCURSALE_TP_SERVICE_EMETTEUR</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$SUCCURSALE_TP_SERVICE_EMETTEUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$TAXE_SERVICES_COMMUNAUX_NUMERO</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable de test</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAXE_SERVICES_COMMUNAUX_NUMERO</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$TAXE_SERVICES_COMMUNAUX_NUMERO</t>
         </is>
       </c>
     </row>
